--- a/tools/보정계산서.xlsx
+++ b/tools/보정계산서.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="사용법" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="s(n) 표" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="평가군 계산" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="종합점수·등급" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="검증" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="예제" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="MIS 요구사항" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="근거 조문" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="s(n) 표" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="평가군 계산" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="종합점수·등급" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검증" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예제" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MIS 요구사항" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="근거 조문" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1112,7 +1112,7 @@
     <row r="2">
       <c r="A2" s="15" t="inlineStr">
         <is>
-          <t>[별표 9] 제3호의 s(n)이다. z가 곧 정규 순서통계량 근사값이므로 s(n)은 그 모표준편차(STDEVP)다. 17명 이상은 [별표 9] 제3호에 따라 s(n) = 1로 본다.</t>
+          <t>[별표 9] 제3호의 s(n)이다. z가 곧 정규 순서통계량 근사값이므로 s(n)은 그 모표준편차(STDEVP)다. s(n)은 해당 평가군 z값들의 표준편차(=STDEVP)다. 인원이 많아도 1로 보지 아니한다.</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="AQ4" s="10" t="inlineStr">
         <is>
-          <t>규정 적용값 (n≥17 → 1)</t>
+          <t>규정 적용값</t>
         </is>
       </c>
       <c r="AR4" s="10" t="inlineStr">
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="AQ5" s="17">
-        <f>IF($A5&gt;=17,1,AP5)</f>
+        <f>AP5</f>
         <v/>
       </c>
       <c r="AR5" s="17" t="n">
@@ -1619,7 +1619,7 @@
         <v/>
       </c>
       <c r="AQ6" s="17">
-        <f>IF($A6&gt;=17,1,AP6)</f>
+        <f>AP6</f>
         <v/>
       </c>
       <c r="AR6" s="17" t="n">
@@ -1799,7 +1799,7 @@
         <v/>
       </c>
       <c r="AQ7" s="17">
-        <f>IF($A7&gt;=17,1,AP7)</f>
+        <f>AP7</f>
         <v/>
       </c>
       <c r="AR7" s="17" t="n">
@@ -1979,7 +1979,7 @@
         <v/>
       </c>
       <c r="AQ8" s="17">
-        <f>IF($A8&gt;=17,1,AP8)</f>
+        <f>AP8</f>
         <v/>
       </c>
       <c r="AR8" s="17" t="n">
@@ -2159,7 +2159,7 @@
         <v/>
       </c>
       <c r="AQ9" s="17">
-        <f>IF($A9&gt;=17,1,AP9)</f>
+        <f>AP9</f>
         <v/>
       </c>
       <c r="AR9" s="17" t="n">
@@ -2339,7 +2339,7 @@
         <v/>
       </c>
       <c r="AQ10" s="17">
-        <f>IF($A10&gt;=17,1,AP10)</f>
+        <f>AP10</f>
         <v/>
       </c>
       <c r="AR10" s="17" t="n">
@@ -2519,7 +2519,7 @@
         <v/>
       </c>
       <c r="AQ11" s="17">
-        <f>IF($A11&gt;=17,1,AP11)</f>
+        <f>AP11</f>
         <v/>
       </c>
       <c r="AR11" s="17" t="n">
@@ -2699,7 +2699,7 @@
         <v/>
       </c>
       <c r="AQ12" s="17">
-        <f>IF($A12&gt;=17,1,AP12)</f>
+        <f>AP12</f>
         <v/>
       </c>
       <c r="AR12" s="17" t="n">
@@ -2879,7 +2879,7 @@
         <v/>
       </c>
       <c r="AQ13" s="17">
-        <f>IF($A13&gt;=17,1,AP13)</f>
+        <f>AP13</f>
         <v/>
       </c>
       <c r="AR13" s="17" t="n">
@@ -3059,7 +3059,7 @@
         <v/>
       </c>
       <c r="AQ14" s="17">
-        <f>IF($A14&gt;=17,1,AP14)</f>
+        <f>AP14</f>
         <v/>
       </c>
       <c r="AR14" s="17" t="n">
@@ -3239,7 +3239,7 @@
         <v/>
       </c>
       <c r="AQ15" s="17">
-        <f>IF($A15&gt;=17,1,AP15)</f>
+        <f>AP15</f>
         <v/>
       </c>
       <c r="AR15" s="17" t="n">
@@ -3419,7 +3419,7 @@
         <v/>
       </c>
       <c r="AQ16" s="17">
-        <f>IF($A16&gt;=17,1,AP16)</f>
+        <f>AP16</f>
         <v/>
       </c>
       <c r="AR16" s="17" t="n">
@@ -3599,7 +3599,7 @@
         <v/>
       </c>
       <c r="AQ17" s="17">
-        <f>IF($A17&gt;=17,1,AP17)</f>
+        <f>AP17</f>
         <v/>
       </c>
       <c r="AR17" s="17" t="n">
@@ -3779,7 +3779,7 @@
         <v/>
       </c>
       <c r="AQ18" s="17">
-        <f>IF($A18&gt;=17,1,AP18)</f>
+        <f>AP18</f>
         <v/>
       </c>
       <c r="AR18" s="17" t="n">
@@ -3959,7 +3959,7 @@
         <v/>
       </c>
       <c r="AQ19" s="17">
-        <f>IF($A19&gt;=17,1,AP19)</f>
+        <f>AP19</f>
         <v/>
       </c>
       <c r="AR19" s="17" t="n">
@@ -4139,7 +4139,7 @@
         <v/>
       </c>
       <c r="AQ20" s="17">
-        <f>IF($A20&gt;=17,1,AP20)</f>
+        <f>AP20</f>
         <v/>
       </c>
       <c r="AR20" s="19" t="inlineStr">
@@ -4322,7 +4322,7 @@
         <v/>
       </c>
       <c r="AQ21" s="17">
-        <f>IF($A21&gt;=17,1,AP21)</f>
+        <f>AP21</f>
         <v/>
       </c>
       <c r="AR21" s="19" t="inlineStr">
@@ -4505,7 +4505,7 @@
         <v/>
       </c>
       <c r="AQ22" s="17">
-        <f>IF($A22&gt;=17,1,AP22)</f>
+        <f>AP22</f>
         <v/>
       </c>
       <c r="AR22" s="19" t="inlineStr">
@@ -4688,7 +4688,7 @@
         <v/>
       </c>
       <c r="AQ23" s="17">
-        <f>IF($A23&gt;=17,1,AP23)</f>
+        <f>AP23</f>
         <v/>
       </c>
       <c r="AR23" s="19" t="inlineStr">
@@ -4871,7 +4871,7 @@
         <v/>
       </c>
       <c r="AQ24" s="17">
-        <f>IF($A24&gt;=17,1,AP24)</f>
+        <f>AP24</f>
         <v/>
       </c>
       <c r="AR24" s="19" t="inlineStr">
@@ -5054,7 +5054,7 @@
         <v/>
       </c>
       <c r="AQ25" s="17">
-        <f>IF($A25&gt;=17,1,AP25)</f>
+        <f>AP25</f>
         <v/>
       </c>
       <c r="AR25" s="19" t="inlineStr">
@@ -5237,7 +5237,7 @@
         <v/>
       </c>
       <c r="AQ26" s="17">
-        <f>IF($A26&gt;=17,1,AP26)</f>
+        <f>AP26</f>
         <v/>
       </c>
       <c r="AR26" s="19" t="inlineStr">
@@ -5420,7 +5420,7 @@
         <v/>
       </c>
       <c r="AQ27" s="17">
-        <f>IF($A27&gt;=17,1,AP27)</f>
+        <f>AP27</f>
         <v/>
       </c>
       <c r="AR27" s="19" t="inlineStr">
@@ -5603,7 +5603,7 @@
         <v/>
       </c>
       <c r="AQ28" s="17">
-        <f>IF($A28&gt;=17,1,AP28)</f>
+        <f>AP28</f>
         <v/>
       </c>
       <c r="AR28" s="19" t="inlineStr">
@@ -5786,7 +5786,7 @@
         <v/>
       </c>
       <c r="AQ29" s="17">
-        <f>IF($A29&gt;=17,1,AP29)</f>
+        <f>AP29</f>
         <v/>
       </c>
       <c r="AR29" s="19" t="inlineStr">
@@ -5969,7 +5969,7 @@
         <v/>
       </c>
       <c r="AQ30" s="17">
-        <f>IF($A30&gt;=17,1,AP30)</f>
+        <f>AP30</f>
         <v/>
       </c>
       <c r="AR30" s="19" t="inlineStr">
@@ -6152,7 +6152,7 @@
         <v/>
       </c>
       <c r="AQ31" s="17">
-        <f>IF($A31&gt;=17,1,AP31)</f>
+        <f>AP31</f>
         <v/>
       </c>
       <c r="AR31" s="19" t="inlineStr">
@@ -6335,7 +6335,7 @@
         <v/>
       </c>
       <c r="AQ32" s="17">
-        <f>IF($A32&gt;=17,1,AP32)</f>
+        <f>AP32</f>
         <v/>
       </c>
       <c r="AR32" s="19" t="inlineStr">
@@ -6518,7 +6518,7 @@
         <v/>
       </c>
       <c r="AQ33" s="17">
-        <f>IF($A33&gt;=17,1,AP33)</f>
+        <f>AP33</f>
         <v/>
       </c>
       <c r="AR33" s="19" t="inlineStr">
@@ -6701,7 +6701,7 @@
         <v/>
       </c>
       <c r="AQ34" s="17">
-        <f>IF($A34&gt;=17,1,AP34)</f>
+        <f>AP34</f>
         <v/>
       </c>
       <c r="AR34" s="19" t="inlineStr">
@@ -6884,7 +6884,7 @@
         <v/>
       </c>
       <c r="AQ35" s="17">
-        <f>IF($A35&gt;=17,1,AP35)</f>
+        <f>AP35</f>
         <v/>
       </c>
       <c r="AR35" s="19" t="inlineStr">
@@ -7067,7 +7067,7 @@
         <v/>
       </c>
       <c r="AQ36" s="17">
-        <f>IF($A36&gt;=17,1,AP36)</f>
+        <f>AP36</f>
         <v/>
       </c>
       <c r="AR36" s="19" t="inlineStr">
@@ -7250,7 +7250,7 @@
         <v/>
       </c>
       <c r="AQ37" s="17">
-        <f>IF($A37&gt;=17,1,AP37)</f>
+        <f>AP37</f>
         <v/>
       </c>
       <c r="AR37" s="19" t="inlineStr">
@@ -7433,7 +7433,7 @@
         <v/>
       </c>
       <c r="AQ38" s="17">
-        <f>IF($A38&gt;=17,1,AP38)</f>
+        <f>AP38</f>
         <v/>
       </c>
       <c r="AR38" s="19" t="inlineStr">
@@ -7616,7 +7616,7 @@
         <v/>
       </c>
       <c r="AQ39" s="17">
-        <f>IF($A39&gt;=17,1,AP39)</f>
+        <f>AP39</f>
         <v/>
       </c>
       <c r="AR39" s="19" t="inlineStr">
@@ -7799,7 +7799,7 @@
         <v/>
       </c>
       <c r="AQ40" s="17">
-        <f>IF($A40&gt;=17,1,AP40)</f>
+        <f>AP40</f>
         <v/>
       </c>
       <c r="AR40" s="19" t="inlineStr">
@@ -7982,7 +7982,7 @@
         <v/>
       </c>
       <c r="AQ41" s="17">
-        <f>IF($A41&gt;=17,1,AP41)</f>
+        <f>AP41</f>
         <v/>
       </c>
       <c r="AR41" s="19" t="inlineStr">
@@ -8165,7 +8165,7 @@
         <v/>
       </c>
       <c r="AQ42" s="17">
-        <f>IF($A42&gt;=17,1,AP42)</f>
+        <f>AP42</f>
         <v/>
       </c>
       <c r="AR42" s="19" t="inlineStr">
@@ -8348,7 +8348,7 @@
         <v/>
       </c>
       <c r="AQ43" s="17">
-        <f>IF($A43&gt;=17,1,AP43)</f>
+        <f>AP43</f>
         <v/>
       </c>
       <c r="AR43" s="19" t="inlineStr">
@@ -8606,7 +8606,7 @@
         <v/>
       </c>
       <c r="I6" s="23">
-        <f>IF($G6&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G6,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G6,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J6" s="17">
@@ -8700,7 +8700,7 @@
         <v/>
       </c>
       <c r="I7" s="23">
-        <f>IF($G7&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G7,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G7,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J7" s="17">
@@ -8794,7 +8794,7 @@
         <v/>
       </c>
       <c r="I8" s="23">
-        <f>IF($G8&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G8,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G8,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J8" s="17">
@@ -8888,7 +8888,7 @@
         <v/>
       </c>
       <c r="I9" s="23">
-        <f>IF($G9&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G9,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G9,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J9" s="17">
@@ -8982,7 +8982,7 @@
         <v/>
       </c>
       <c r="I10" s="23">
-        <f>IF($G10&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G10,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G10,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J10" s="17">
@@ -9072,7 +9072,7 @@
         <v/>
       </c>
       <c r="I11" s="23">
-        <f>IF($G11&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G11,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G11,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J11" s="17">
@@ -9162,7 +9162,7 @@
         <v/>
       </c>
       <c r="I12" s="23">
-        <f>IF($G12&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G12,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G12,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J12" s="17">
@@ -9256,7 +9256,7 @@
         <v/>
       </c>
       <c r="I13" s="23">
-        <f>IF($G13&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G13,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G13,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J13" s="17">
@@ -9350,7 +9350,7 @@
         <v/>
       </c>
       <c r="I14" s="23">
-        <f>IF($G14&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G14,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G14,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J14" s="17">
@@ -9444,7 +9444,7 @@
         <v/>
       </c>
       <c r="I15" s="23">
-        <f>IF($G15&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G15,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G15,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J15" s="17">
@@ -9538,7 +9538,7 @@
         <v/>
       </c>
       <c r="I16" s="23">
-        <f>IF($G16&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G16,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G16,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J16" s="17">
@@ -9632,7 +9632,7 @@
         <v/>
       </c>
       <c r="I17" s="23">
-        <f>IF($G17&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G17,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G17,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J17" s="17">
@@ -9726,7 +9726,7 @@
         <v/>
       </c>
       <c r="I18" s="23">
-        <f>IF($G18&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G18,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G18,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J18" s="17">
@@ -9820,7 +9820,7 @@
         <v/>
       </c>
       <c r="I19" s="23">
-        <f>IF($G19&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G19,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G19,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J19" s="17">
@@ -9914,7 +9914,7 @@
         <v/>
       </c>
       <c r="I20" s="23">
-        <f>IF($G20&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G20,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G20,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J20" s="17">
@@ -10004,7 +10004,7 @@
         <v/>
       </c>
       <c r="I21" s="23">
-        <f>IF($G21&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G21,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G21,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J21" s="17">
@@ -10094,7 +10094,7 @@
         <v/>
       </c>
       <c r="I22" s="23">
-        <f>IF($G22&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G22,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G22,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J22" s="17">
@@ -10184,7 +10184,7 @@
         <v/>
       </c>
       <c r="I23" s="23">
-        <f>IF($G23&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G23,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G23,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J23" s="17">
@@ -10274,7 +10274,7 @@
         <v/>
       </c>
       <c r="I24" s="23">
-        <f>IF($G24&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G24,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G24,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J24" s="17">
@@ -10364,7 +10364,7 @@
         <v/>
       </c>
       <c r="I25" s="23">
-        <f>IF($G25&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G25,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G25,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J25" s="17">
@@ -10454,7 +10454,7 @@
         <v/>
       </c>
       <c r="I26" s="23">
-        <f>IF($G26&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G26,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G26,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J26" s="17">
@@ -10544,7 +10544,7 @@
         <v/>
       </c>
       <c r="I27" s="23">
-        <f>IF($G27&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G27,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G27,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J27" s="17">
@@ -10634,7 +10634,7 @@
         <v/>
       </c>
       <c r="I28" s="23">
-        <f>IF($G28&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G28,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G28,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J28" s="17">
@@ -10724,7 +10724,7 @@
         <v/>
       </c>
       <c r="I29" s="23">
-        <f>IF($G29&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G29,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G29,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J29" s="17">
@@ -10814,7 +10814,7 @@
         <v/>
       </c>
       <c r="I30" s="23">
-        <f>IF($G30&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G30,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G30,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J30" s="17">
@@ -10904,7 +10904,7 @@
         <v/>
       </c>
       <c r="I31" s="23">
-        <f>IF($G31&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G31,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G31,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J31" s="17">
@@ -10994,7 +10994,7 @@
         <v/>
       </c>
       <c r="I32" s="23">
-        <f>IF($G32&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G32,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G32,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J32" s="17">
@@ -11084,7 +11084,7 @@
         <v/>
       </c>
       <c r="I33" s="23">
-        <f>IF($G33&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G33,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G33,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J33" s="17">
@@ -11174,7 +11174,7 @@
         <v/>
       </c>
       <c r="I34" s="23">
-        <f>IF($G34&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G34,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G34,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J34" s="17">
@@ -11264,7 +11264,7 @@
         <v/>
       </c>
       <c r="I35" s="23">
-        <f>IF($G35&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G35,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G35,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J35" s="17">
@@ -11354,7 +11354,7 @@
         <v/>
       </c>
       <c r="I36" s="23">
-        <f>IF($G36&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G36,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G36,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J36" s="17">
@@ -11448,7 +11448,7 @@
         <v/>
       </c>
       <c r="I37" s="23">
-        <f>IF($G37&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G37,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G37,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J37" s="17">
@@ -11542,7 +11542,7 @@
         <v/>
       </c>
       <c r="I38" s="23">
-        <f>IF($G38&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G38,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G38,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J38" s="17">
@@ -11636,7 +11636,7 @@
         <v/>
       </c>
       <c r="I39" s="23">
-        <f>IF($G39&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G39,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G39,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J39" s="17">
@@ -11730,7 +11730,7 @@
         <v/>
       </c>
       <c r="I40" s="23">
-        <f>IF($G40&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G40,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G40,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J40" s="17">
@@ -11824,7 +11824,7 @@
         <v/>
       </c>
       <c r="I41" s="23">
-        <f>IF($G41&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G41,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G41,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J41" s="17">
@@ -11918,7 +11918,7 @@
         <v/>
       </c>
       <c r="I42" s="23">
-        <f>IF($G42&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G42,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G42,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J42" s="17">
@@ -12012,7 +12012,7 @@
         <v/>
       </c>
       <c r="I43" s="23">
-        <f>IF($G43&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G43,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G43,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J43" s="17">
@@ -12106,7 +12106,7 @@
         <v/>
       </c>
       <c r="I44" s="23">
-        <f>IF($G44&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G44,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G44,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J44" s="17">
@@ -12200,7 +12200,7 @@
         <v/>
       </c>
       <c r="I45" s="23">
-        <f>IF($G45&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G45,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G45,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J45" s="17">
@@ -12294,7 +12294,7 @@
         <v/>
       </c>
       <c r="I46" s="23">
-        <f>IF($G46&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G46,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G46,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J46" s="17">
@@ -12388,7 +12388,7 @@
         <v/>
       </c>
       <c r="I47" s="23">
-        <f>IF($G47&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G47,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G47,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J47" s="17">
@@ -12482,7 +12482,7 @@
         <v/>
       </c>
       <c r="I48" s="23">
-        <f>IF($G48&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G48,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G48,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J48" s="17">
@@ -12576,7 +12576,7 @@
         <v/>
       </c>
       <c r="I49" s="23">
-        <f>IF($G49&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G49,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G49,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J49" s="17">
@@ -12670,7 +12670,7 @@
         <v/>
       </c>
       <c r="I50" s="23">
-        <f>IF($G50&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G50,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G50,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J50" s="17">
@@ -12764,7 +12764,7 @@
         <v/>
       </c>
       <c r="I51" s="23">
-        <f>IF($G51&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G51,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G51,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J51" s="17">
@@ -12858,7 +12858,7 @@
         <v/>
       </c>
       <c r="I52" s="23">
-        <f>IF($G52&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G52,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G52,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J52" s="17">
@@ -12952,7 +12952,7 @@
         <v/>
       </c>
       <c r="I53" s="23">
-        <f>IF($G53&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G53,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G53,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J53" s="17">
@@ -13046,7 +13046,7 @@
         <v/>
       </c>
       <c r="I54" s="23">
-        <f>IF($G54&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G54,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G54,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J54" s="17">
@@ -13140,7 +13140,7 @@
         <v/>
       </c>
       <c r="I55" s="23">
-        <f>IF($G55&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G55,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G55,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J55" s="17">
@@ -13234,7 +13234,7 @@
         <v/>
       </c>
       <c r="I56" s="23">
-        <f>IF($G56&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G56,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G56,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J56" s="17">
@@ -13328,7 +13328,7 @@
         <v/>
       </c>
       <c r="I57" s="23">
-        <f>IF($G57&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G57,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G57,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J57" s="17">
@@ -13422,7 +13422,7 @@
         <v/>
       </c>
       <c r="I58" s="23">
-        <f>IF($G58&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G58,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G58,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J58" s="17">
@@ -13516,7 +13516,7 @@
         <v/>
       </c>
       <c r="I59" s="23">
-        <f>IF($G59&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G59,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G59,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J59" s="17">
@@ -13610,7 +13610,7 @@
         <v/>
       </c>
       <c r="I60" s="23">
-        <f>IF($G60&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G60,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G60,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J60" s="17">
@@ -13704,7 +13704,7 @@
         <v/>
       </c>
       <c r="I61" s="23">
-        <f>IF($G61&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G61,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G61,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J61" s="17">
@@ -13798,7 +13798,7 @@
         <v/>
       </c>
       <c r="I62" s="23">
-        <f>IF($G62&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G62,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G62,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J62" s="17">
@@ -13892,7 +13892,7 @@
         <v/>
       </c>
       <c r="I63" s="23">
-        <f>IF($G63&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G63,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G63,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J63" s="17">
@@ -13986,7 +13986,7 @@
         <v/>
       </c>
       <c r="I64" s="23">
-        <f>IF($G64&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G64,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G64,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J64" s="17">
@@ -14080,7 +14080,7 @@
         <v/>
       </c>
       <c r="I65" s="23">
-        <f>IF($G65&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G65,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G65,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J65" s="17">
@@ -14174,7 +14174,7 @@
         <v/>
       </c>
       <c r="I66" s="23">
-        <f>IF($G66&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G66,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G66,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J66" s="17">
@@ -14268,7 +14268,7 @@
         <v/>
       </c>
       <c r="I67" s="23">
-        <f>IF($G67&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G67,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G67,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J67" s="17">
@@ -14362,7 +14362,7 @@
         <v/>
       </c>
       <c r="I68" s="23">
-        <f>IF($G68&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G68,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G68,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J68" s="17">
@@ -14452,7 +14452,7 @@
         <v/>
       </c>
       <c r="I69" s="23">
-        <f>IF($G69&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G69,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G69,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J69" s="17">
@@ -14542,7 +14542,7 @@
         <v/>
       </c>
       <c r="I70" s="23">
-        <f>IF($G70&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G70,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G70,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J70" s="17">
@@ -14632,7 +14632,7 @@
         <v/>
       </c>
       <c r="I71" s="23">
-        <f>IF($G71&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G71,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G71,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J71" s="17">
@@ -14726,7 +14726,7 @@
         <v/>
       </c>
       <c r="I72" s="23">
-        <f>IF($G72&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G72,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G72,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J72" s="17">
@@ -14820,7 +14820,7 @@
         <v/>
       </c>
       <c r="I73" s="23">
-        <f>IF($G73&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G73,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G73,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J73" s="17">
@@ -14914,7 +14914,7 @@
         <v/>
       </c>
       <c r="I74" s="23">
-        <f>IF($G74&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G74,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G74,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J74" s="17">
@@ -15008,7 +15008,7 @@
         <v/>
       </c>
       <c r="I75" s="23">
-        <f>IF($G75&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G75,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G75,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J75" s="17">
@@ -15102,7 +15102,7 @@
         <v/>
       </c>
       <c r="I76" s="23">
-        <f>IF($G76&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G76,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G76,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J76" s="17">
@@ -15196,7 +15196,7 @@
         <v/>
       </c>
       <c r="I77" s="23">
-        <f>IF($G77&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G77,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G77,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J77" s="17">
@@ -15290,7 +15290,7 @@
         <v/>
       </c>
       <c r="I78" s="23">
-        <f>IF($G78&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G78,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G78,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J78" s="17">
@@ -15384,7 +15384,7 @@
         <v/>
       </c>
       <c r="I79" s="23">
-        <f>IF($G79&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G79,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($G79,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="J79" s="17">
@@ -15790,7 +15790,7 @@
         <v/>
       </c>
       <c r="O9" s="23">
-        <f>IF($L9&lt;3,"",IF($M9&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M9,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L9&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M9,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P9" s="24">
@@ -15912,7 +15912,7 @@
         <v/>
       </c>
       <c r="O10" s="23">
-        <f>IF($L10&lt;3,"",IF($M10&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M10,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L10&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M10,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P10" s="24">
@@ -16034,7 +16034,7 @@
         <v/>
       </c>
       <c r="O11" s="23">
-        <f>IF($L11&lt;3,"",IF($M11&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M11,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L11&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M11,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P11" s="24">
@@ -16156,7 +16156,7 @@
         <v/>
       </c>
       <c r="O12" s="23">
-        <f>IF($L12&lt;3,"",IF($M12&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M12,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L12&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M12,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P12" s="24">
@@ -16278,7 +16278,7 @@
         <v/>
       </c>
       <c r="O13" s="23">
-        <f>IF($L13&lt;3,"",IF($M13&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M13,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L13&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M13,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P13" s="24">
@@ -16400,7 +16400,7 @@
         <v/>
       </c>
       <c r="O14" s="23">
-        <f>IF($L14&lt;3,"",IF($M14&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M14,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L14&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M14,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P14" s="24">
@@ -16522,7 +16522,7 @@
         <v/>
       </c>
       <c r="O15" s="23">
-        <f>IF($L15&lt;3,"",IF($M15&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M15,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L15&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M15,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P15" s="24">
@@ -16644,7 +16644,7 @@
         <v/>
       </c>
       <c r="O16" s="23">
-        <f>IF($L16&lt;3,"",IF($M16&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M16,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L16&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M16,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P16" s="24">
@@ -16766,7 +16766,7 @@
         <v/>
       </c>
       <c r="O17" s="23">
-        <f>IF($L17&lt;3,"",IF($M17&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M17,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L17&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M17,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P17" s="24">
@@ -16888,7 +16888,7 @@
         <v/>
       </c>
       <c r="O18" s="23">
-        <f>IF($L18&lt;3,"",IF($M18&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M18,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L18&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M18,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P18" s="24">
@@ -17010,7 +17010,7 @@
         <v/>
       </c>
       <c r="O19" s="23">
-        <f>IF($L19&lt;3,"",IF($M19&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M19,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L19&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M19,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P19" s="24">
@@ -17132,7 +17132,7 @@
         <v/>
       </c>
       <c r="O20" s="23">
-        <f>IF($L20&lt;3,"",IF($M20&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M20,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L20&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M20,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P20" s="24">
@@ -17254,7 +17254,7 @@
         <v/>
       </c>
       <c r="O21" s="23">
-        <f>IF($L21&lt;3,"",IF($M21&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M21,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L21&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M21,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P21" s="24">
@@ -17376,7 +17376,7 @@
         <v/>
       </c>
       <c r="O22" s="23">
-        <f>IF($L22&lt;3,"",IF($M22&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M22,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L22&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M22,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P22" s="24">
@@ -17498,7 +17498,7 @@
         <v/>
       </c>
       <c r="O23" s="23">
-        <f>IF($L23&lt;3,"",IF($M23&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M23,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L23&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M23,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P23" s="24">
@@ -17620,7 +17620,7 @@
         <v/>
       </c>
       <c r="O24" s="23">
-        <f>IF($L24&lt;3,"",IF($M24&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M24,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L24&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M24,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P24" s="24">
@@ -17742,7 +17742,7 @@
         <v/>
       </c>
       <c r="O25" s="23">
-        <f>IF($L25&lt;3,"",IF($M25&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M25,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L25&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M25,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P25" s="24">
@@ -17864,7 +17864,7 @@
         <v/>
       </c>
       <c r="O26" s="23">
-        <f>IF($L26&lt;3,"",IF($M26&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M26,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L26&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M26,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P26" s="24">
@@ -17986,7 +17986,7 @@
         <v/>
       </c>
       <c r="O27" s="23">
-        <f>IF($L27&lt;3,"",IF($M27&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M27,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L27&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M27,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P27" s="24">
@@ -18108,7 +18108,7 @@
         <v/>
       </c>
       <c r="O28" s="23">
-        <f>IF($L28&lt;3,"",IF($M28&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M28,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L28&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M28,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P28" s="24">
@@ -18230,7 +18230,7 @@
         <v/>
       </c>
       <c r="O29" s="23">
-        <f>IF($L29&lt;3,"",IF($M29&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M29,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L29&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M29,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P29" s="24">
@@ -18352,7 +18352,7 @@
         <v/>
       </c>
       <c r="O30" s="23">
-        <f>IF($L30&lt;3,"",IF($M30&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M30,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L30&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M30,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P30" s="24">
@@ -18474,7 +18474,7 @@
         <v/>
       </c>
       <c r="O31" s="23">
-        <f>IF($L31&lt;3,"",IF($M31&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M31,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L31&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M31,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P31" s="24">
@@ -18596,7 +18596,7 @@
         <v/>
       </c>
       <c r="O32" s="23">
-        <f>IF($L32&lt;3,"",IF($M32&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M32,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L32&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M32,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P32" s="24">
@@ -18718,7 +18718,7 @@
         <v/>
       </c>
       <c r="O33" s="23">
-        <f>IF($L33&lt;3,"",IF($M33&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M33,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L33&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M33,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P33" s="24">
@@ -18840,7 +18840,7 @@
         <v/>
       </c>
       <c r="O34" s="23">
-        <f>IF($L34&lt;3,"",IF($M34&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M34,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L34&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M34,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P34" s="24">
@@ -18962,7 +18962,7 @@
         <v/>
       </c>
       <c r="O35" s="23">
-        <f>IF($L35&lt;3,"",IF($M35&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M35,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L35&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M35,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P35" s="24">
@@ -19084,7 +19084,7 @@
         <v/>
       </c>
       <c r="O36" s="23">
-        <f>IF($L36&lt;3,"",IF($M36&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M36,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L36&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M36,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P36" s="24">
@@ -19206,7 +19206,7 @@
         <v/>
       </c>
       <c r="O37" s="23">
-        <f>IF($L37&lt;3,"",IF($M37&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M37,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L37&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M37,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P37" s="24">
@@ -19328,7 +19328,7 @@
         <v/>
       </c>
       <c r="O38" s="23">
-        <f>IF($L38&lt;3,"",IF($M38&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M38,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L38&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M38,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P38" s="24">
@@ -19450,7 +19450,7 @@
         <v/>
       </c>
       <c r="O39" s="23">
-        <f>IF($L39&lt;3,"",IF($M39&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M39,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L39&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M39,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P39" s="24">
@@ -19572,7 +19572,7 @@
         <v/>
       </c>
       <c r="O40" s="23">
-        <f>IF($L40&lt;3,"",IF($M40&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M40,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L40&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M40,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P40" s="24">
@@ -19694,7 +19694,7 @@
         <v/>
       </c>
       <c r="O41" s="23">
-        <f>IF($L41&lt;3,"",IF($M41&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M41,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L41&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M41,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P41" s="24">
@@ -19816,7 +19816,7 @@
         <v/>
       </c>
       <c r="O42" s="23">
-        <f>IF($L42&lt;3,"",IF($M42&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M42,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L42&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M42,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P42" s="24">
@@ -19938,7 +19938,7 @@
         <v/>
       </c>
       <c r="O43" s="23">
-        <f>IF($L43&lt;3,"",IF($M43&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M43,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L43&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M43,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P43" s="24">
@@ -20060,7 +20060,7 @@
         <v/>
       </c>
       <c r="O44" s="23">
-        <f>IF($L44&lt;3,"",IF($M44&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M44,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L44&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M44,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P44" s="24">
@@ -20180,7 +20180,7 @@
         <v/>
       </c>
       <c r="O45" s="23">
-        <f>IF($L45&lt;3,"",IF($M45&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M45,'s(n) 표'!$A$5:$A$43,0))))</f>
+        <f>IF($L45&lt;3,"",INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($M45,'s(n) 표'!$A$5:$A$43,0)))</f>
         <v/>
       </c>
       <c r="P45" s="24">
@@ -20600,7 +20600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -20732,9 +20732,8 @@
         <f>ROUND(STDEVP('평가군 계산'!$L$6:$L$15),2)</f>
         <v/>
       </c>
-      <c r="G7" s="27">
-        <f>IF($C7&lt;=16,7,IFERROR(ROUND(7*INDEX('s(n) 표'!$AP$5:$AP$43,MATCH($C7,'s(n) 표'!$A$5:$A$43,0)),2),"④ 표(n≤40) 확장 필요"))</f>
-        <v/>
+      <c r="G7" s="27" t="n">
+        <v>7</v>
       </c>
       <c r="H7" s="19">
         <f>IF($F7=$G7,"PASS","FAIL")</f>
@@ -20832,9 +20831,8 @@
         <f>ROUND(STDEVP('평가군 계산'!$L$20:$L$35),2)</f>
         <v/>
       </c>
-      <c r="G9" s="27">
-        <f>IF($C9&lt;=16,7,IFERROR(ROUND(7*INDEX('s(n) 표'!$AP$5:$AP$43,MATCH($C9,'s(n) 표'!$A$5:$A$43,0)),2),"④ 표(n≤40) 확장 필요"))</f>
-        <v/>
+      <c r="G9" s="27" t="n">
+        <v>7</v>
       </c>
       <c r="H9" s="19">
         <f>IF($F9=$G9,"PASS","FAIL")</f>
@@ -20879,9 +20877,8 @@
         <f>ROUND(STDEVP('평가군 계산'!$L$36:$L$65),2)</f>
         <v/>
       </c>
-      <c r="G10" s="27">
-        <f>IF($C10&lt;=16,7,IFERROR(ROUND(7*INDEX('s(n) 표'!$AP$5:$AP$43,MATCH($C10,'s(n) 표'!$A$5:$A$43,0)),2),"④ 표(n≤40) 확장 필요"))</f>
-        <v/>
+      <c r="G10" s="27" t="n">
+        <v>7</v>
       </c>
       <c r="H10" s="19">
         <f>IF($F10=$G10,"PASS","FAIL")</f>
@@ -20926,9 +20923,8 @@
         <f>ROUND(STDEVP('평가군 계산'!$L$66:$L$72),2)</f>
         <v/>
       </c>
-      <c r="G11" s="27">
-        <f>IF($C11&lt;=16,7,IFERROR(ROUND(7*INDEX('s(n) 표'!$AP$5:$AP$43,MATCH($C11,'s(n) 표'!$A$5:$A$43,0)),2),"④ 표(n≤40) 확장 필요"))</f>
-        <v/>
+      <c r="G11" s="27" t="n">
+        <v>7</v>
       </c>
       <c r="H11" s="19">
         <f>IF($F11=$G11,"PASS","FAIL")</f>
@@ -20973,9 +20969,8 @@
         <f>ROUND(STDEVP('평가군 계산'!$L$73:$L$79),2)</f>
         <v/>
       </c>
-      <c r="G12" s="27">
-        <f>IF($C12&lt;=16,7,IFERROR(ROUND(7*INDEX('s(n) 표'!$AP$5:$AP$43,MATCH($C12,'s(n) 표'!$A$5:$A$43,0)),2),"④ 표(n≤40) 확장 필요"))</f>
-        <v/>
+      <c r="G12" s="27" t="n">
+        <v>7</v>
       </c>
       <c r="H12" s="19">
         <f>IF($F12=$G12,"PASS","FAIL")</f>
@@ -21004,14 +20999,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>1-2. 조합이 먼저 밝히는 논점 — 제3호 후단 「17명 이상은 s(n) = 1로 본다」의 효과</t>
+          <t>1-2. ÷ s(n) 이 왜 필요한가 — 1차와 2차의 척도를 맞춘다</t>
         </is>
       </c>
     </row>
     <row r="16" ht="44" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>1차 평가군(부서 단위)은 창업진흥원에서 3~16명이므로 s(n) 표가 적용되어 표준편차가 정확히 7.00이 된다. 그러나 2차 평가군(본부 단위)은 통상 17명 이상이어서 제3호 후단에 따라 s(n)=1 이 적용되고, 표준편차가 7.00에 미달한다. 아래 값은 모두 ④ 시트에서 계산된 것이다.</t>
+          <t>[별표 9] 제3호는 인원과 무관하게 z를 s(n)으로 나눈다. 그 결과 1차 평가군(부서 3~16명)과 2차 평가군(본부 33~59명)이 모두 표준편차 7.00이 된다. 나눗셈이 없으면 인원이 적을수록 표준편차가 작아져 1차와 2차의 척도가 어긋나고, [별표 2]의 60:40 가중이 의도한 비중대로 작동하지 않는다. 아래 값은 모두 ④ 시트에서 계산된 것이다.</t>
         </is>
       </c>
     </row>
@@ -21023,230 +21018,231 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>s(n) 실제값 (④ 시트)</t>
+          <t>s(n) (④ 시트)</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>제3호 후단 적용 s(n)</t>
+          <t>÷ s(n) 없을 때 표준편차</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>그때의 표준편차 = 7×s(n)</t>
+          <t>목표 7.00과의 차</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>목표 7.00과의 차</t>
+          <t>÷ s(n) 적용</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>s(n) 표를 그대로 쓰면</t>
+          <t>판정</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="19" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B18" s="23">
         <f>INDEX('s(n) 표'!$AP$5:$AP$43,MATCH($A18,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
-      <c r="C18" s="23">
-        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($A18,'s(n) 표'!$A$5:$A$43,0))</f>
-        <v/>
-      </c>
-      <c r="D18" s="27">
-        <f>ROUND(7*$B18/$C18,2)</f>
-        <v/>
-      </c>
-      <c r="E18" s="30">
-        <f>ROUND($D18-7,2)</f>
-        <v/>
-      </c>
-      <c r="F18" s="27">
+      <c r="C18" s="27">
+        <f>ROUND(7*$B18,2)</f>
+        <v/>
+      </c>
+      <c r="D18" s="30">
+        <f>ROUND($C18-7,2)</f>
+        <v/>
+      </c>
+      <c r="E18" s="27">
         <f>ROUND(7*$B18/$B18,2)</f>
+        <v/>
+      </c>
+      <c r="F18" s="19">
+        <f>IF($E18=7,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="19" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B19" s="23">
         <f>INDEX('s(n) 표'!$AP$5:$AP$43,MATCH($A19,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
-      <c r="C19" s="23">
-        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($A19,'s(n) 표'!$A$5:$A$43,0))</f>
-        <v/>
-      </c>
-      <c r="D19" s="27">
-        <f>ROUND(7*$B19/$C19,2)</f>
-        <v/>
-      </c>
-      <c r="E19" s="30">
-        <f>ROUND($D19-7,2)</f>
-        <v/>
-      </c>
-      <c r="F19" s="27">
+      <c r="C19" s="27">
+        <f>ROUND(7*$B19,2)</f>
+        <v/>
+      </c>
+      <c r="D19" s="30">
+        <f>ROUND($C19-7,2)</f>
+        <v/>
+      </c>
+      <c r="E19" s="27">
         <f>ROUND(7*$B19/$B19,2)</f>
+        <v/>
+      </c>
+      <c r="F19" s="19">
+        <f>IF($E19=7,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="19" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B20" s="23">
         <f>INDEX('s(n) 표'!$AP$5:$AP$43,MATCH($A20,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
-      <c r="C20" s="23">
-        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($A20,'s(n) 표'!$A$5:$A$43,0))</f>
-        <v/>
-      </c>
-      <c r="D20" s="27">
-        <f>ROUND(7*$B20/$C20,2)</f>
-        <v/>
-      </c>
-      <c r="E20" s="30">
-        <f>ROUND($D20-7,2)</f>
-        <v/>
-      </c>
-      <c r="F20" s="27">
+      <c r="C20" s="27">
+        <f>ROUND(7*$B20,2)</f>
+        <v/>
+      </c>
+      <c r="D20" s="30">
+        <f>ROUND($C20-7,2)</f>
+        <v/>
+      </c>
+      <c r="E20" s="27">
         <f>ROUND(7*$B20/$B20,2)</f>
+        <v/>
+      </c>
+      <c r="F20" s="19">
+        <f>IF($E20=7,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B21" s="23">
         <f>INDEX('s(n) 표'!$AP$5:$AP$43,MATCH($A21,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
-      <c r="C21" s="23">
-        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($A21,'s(n) 표'!$A$5:$A$43,0))</f>
-        <v/>
-      </c>
-      <c r="D21" s="27">
-        <f>ROUND(7*$B21/$C21,2)</f>
-        <v/>
-      </c>
-      <c r="E21" s="30">
-        <f>ROUND($D21-7,2)</f>
-        <v/>
-      </c>
-      <c r="F21" s="27">
+      <c r="C21" s="27">
+        <f>ROUND(7*$B21,2)</f>
+        <v/>
+      </c>
+      <c r="D21" s="30">
+        <f>ROUND($C21-7,2)</f>
+        <v/>
+      </c>
+      <c r="E21" s="27">
         <f>ROUND(7*$B21/$B21,2)</f>
+        <v/>
+      </c>
+      <c r="F21" s="19">
+        <f>IF($E21=7,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="19" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B22" s="23">
         <f>INDEX('s(n) 표'!$AP$5:$AP$43,MATCH($A22,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
-      <c r="C22" s="23">
-        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($A22,'s(n) 표'!$A$5:$A$43,0))</f>
-        <v/>
-      </c>
-      <c r="D22" s="27">
-        <f>ROUND(7*$B22/$C22,2)</f>
-        <v/>
-      </c>
-      <c r="E22" s="30">
-        <f>ROUND($D22-7,2)</f>
-        <v/>
-      </c>
-      <c r="F22" s="27">
+      <c r="C22" s="27">
+        <f>ROUND(7*$B22,2)</f>
+        <v/>
+      </c>
+      <c r="D22" s="30">
+        <f>ROUND($C22-7,2)</f>
+        <v/>
+      </c>
+      <c r="E22" s="27">
         <f>ROUND(7*$B22/$B22,2)</f>
         <v/>
       </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="31" t="inlineStr">
-        <is>
-          <t>해소 방법 — ④ 시트는 이미 n = 40까지 s(n)을 수식으로 계산해 두었다. [별표 9] 제3호 후단을 삭제하고 s(n) 표를 인원 구간 전체로 확대하면 F열처럼 전 구간에서 7.00이 된다(조문 한 줄). 그대로 두는 경우에도 1차 평가군은 영향을 받지 않으며, 2차 평가군의 표준편차가 약 6.5~6.8점이 되어 2차 평가자의 점수 폭이 1차보다 조금 좁아진다는 뜻이다. 어느 쪽을 택할지는 노사 협의 사항이다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="F22" s="19">
+        <f>IF($E22=7,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="B23" s="23">
+        <f>INDEX('s(n) 표'!$AP$5:$AP$43,MATCH($A23,'s(n) 표'!$A$5:$A$43,0))</f>
+        <v/>
+      </c>
+      <c r="C23" s="27">
+        <f>ROUND(7*$B23,2)</f>
+        <v/>
+      </c>
+      <c r="D23" s="30">
+        <f>ROUND($C23-7,2)</f>
+        <v/>
+      </c>
+      <c r="E23" s="27">
+        <f>ROUND(7*$B23/$B23,2)</f>
+        <v/>
+      </c>
+      <c r="F23" s="19">
+        <f>IF($E23=7,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>C열이 ÷ s(n) 없이 계산한 표준편차이며 인원이 적을수록 7.00에 미달한다(3명 4.97 · 10명 6.24 · 16명 6.49 · 본부 규모 6.70~6.83). E열이 [별표 9] 제3호를 적용한 값이며 전 구간에서 7.00이다. 엑셀에서는 =STDEVP(z값 범위) 한 줄로 산출되므로 표에 없는 인원도 같은 방법으로 계산한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>2. ÷s(n) 의 효과 — 나눗셈이 없으면 어느 평가군도 제4호의 표준편차 7점을 달성하지 못한다</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="34" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>평가군 인원 n</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>s(n)  (④ 시트 참조)</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>÷s(n) 없을 때 표준편차
 = 7 × s(n)</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>÷s(n) 적용 시 표준편차
 = 7 × s(n) ÷ s(n)</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E27" s="10" t="inlineStr">
         <is>
           <t>개정안 명시값</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>판정</t>
         </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="B27" s="23">
-        <f>INDEX('s(n) 표'!$AP$5:$AP$43,MATCH($A27,'s(n) 표'!$A$5:$A$43,0))</f>
-        <v/>
-      </c>
-      <c r="C27" s="27">
-        <f>ROUND(7*$B27,2)</f>
-        <v/>
-      </c>
-      <c r="D27" s="27">
-        <f>ROUND(7*$B27/$B27,2)</f>
-        <v/>
-      </c>
-      <c r="E27" s="27" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="F27" s="19">
-        <f>IF(AND($C27=$E27,$D27=7),"PASS","FAIL")</f>
-        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B28" s="23">
         <f>INDEX('s(n) 표'!$AP$5:$AP$43,MATCH($A28,'s(n) 표'!$A$5:$A$43,0))</f>
@@ -21261,7 +21257,7 @@
         <v/>
       </c>
       <c r="E28" s="27" t="n">
-        <v>5.67</v>
+        <v>4.97</v>
       </c>
       <c r="F28" s="19">
         <f>IF(AND($C28=$E28,$D28=7),"PASS","FAIL")</f>
@@ -21270,7 +21266,7 @@
     </row>
     <row r="29">
       <c r="A29" s="19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B29" s="23">
         <f>INDEX('s(n) 표'!$AP$5:$AP$43,MATCH($A29,'s(n) 표'!$A$5:$A$43,0))</f>
@@ -21285,7 +21281,7 @@
         <v/>
       </c>
       <c r="E29" s="27" t="n">
-        <v>6.24</v>
+        <v>5.67</v>
       </c>
       <c r="F29" s="19">
         <f>IF(AND($C29=$E29,$D29=7),"PASS","FAIL")</f>
@@ -21294,7 +21290,7 @@
     </row>
     <row r="30">
       <c r="A30" s="19" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B30" s="23">
         <f>INDEX('s(n) 표'!$AP$5:$AP$43,MATCH($A30,'s(n) 표'!$A$5:$A$43,0))</f>
@@ -21309,7 +21305,7 @@
         <v/>
       </c>
       <c r="E30" s="27" t="n">
-        <v>6.49</v>
+        <v>6.24</v>
       </c>
       <c r="F30" s="19">
         <f>IF(AND($C30=$E30,$D30=7),"PASS","FAIL")</f>
@@ -21317,67 +21313,73 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="B31" s="23">
+        <f>INDEX('s(n) 표'!$AP$5:$AP$43,MATCH($A31,'s(n) 표'!$A$5:$A$43,0))</f>
+        <v/>
+      </c>
+      <c r="C31" s="27">
+        <f>ROUND(7*$B31,2)</f>
+        <v/>
+      </c>
+      <c r="D31" s="27">
+        <f>ROUND(7*$B31/$B31,2)</f>
+        <v/>
+      </c>
+      <c r="E31" s="27" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="F31" s="19">
+        <f>IF(AND($C31=$E31,$D31=7),"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>E열은 개정안 [별표 9] ÷s(n) 설명표의 값(4.97 / 5.67 / 6.24 / 6.49)이다. C열이 그 값을 재현한다.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>3. 부서 내 순위 보존 · 절단 · 동점 · s(n) 표</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>검증 항목</t>
         </is>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>산출값</t>
         </is>
       </c>
-      <c r="C34" s="10" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>요구값</t>
         </is>
       </c>
-      <c r="D34" s="10" t="inlineStr">
+      <c r="D35" s="10" t="inlineStr">
         <is>
           <t>판정</t>
         </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>원점수 순위 ≠ 보정 후 순위 인 건수 (순위 100% 보존)</t>
-        </is>
-      </c>
-      <c r="B35" s="19">
-        <f>COUNTIF('평가군 계산'!$S$6:$S$79,"★불일치")</f>
-        <v/>
-      </c>
-      <c r="C35" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="19">
-        <f>IF($B35=$C35,"PASS","FAIL")</f>
-        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>동점 입력 건수 (개정 2 — 동점 금지)</t>
+          <t>원점수 순위 ≠ 보정 후 순위 인 건수 (순위 100% 보존)</t>
         </is>
       </c>
       <c r="B36" s="19">
-        <f>COUNTIF('평가군 계산'!$Q$6:$Q$79,"★동점")</f>
+        <f>COUNTIF('평가군 계산'!$S$6:$S$79,"★불일치")</f>
         <v/>
       </c>
       <c r="C36" s="19" t="n">
@@ -21391,11 +21393,11 @@
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>보정점수 절단(60점 미만) 발생 건수 — ② U열 기준</t>
+          <t>동점 입력 건수 (개정 2 — 동점 금지)</t>
         </is>
       </c>
       <c r="B37" s="19">
-        <f>COUNTIF('평가군 계산'!$U$6:$U$79,"&lt;60")</f>
+        <f>COUNTIF('평가군 계산'!$Q$6:$Q$79,"★동점")</f>
         <v/>
       </c>
       <c r="C37" s="19" t="n">
@@ -21409,11 +21411,11 @@
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>보정점수 절단(100점 초과) 발생 건수 — ② U열 기준</t>
+          <t>보정점수 절단(60점 미만) 발생 건수 — ② U열 기준</t>
         </is>
       </c>
       <c r="B38" s="19">
-        <f>COUNTIF('평가군 계산'!$U$6:$U$79,"&gt;100")</f>
+        <f>COUNTIF('평가군 계산'!$U$6:$U$79,"&lt;60")</f>
         <v/>
       </c>
       <c r="C38" s="19" t="n">
@@ -21427,11 +21429,11 @@
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>제7호 조정 후 절단 발생 건수 — ② V열 기준</t>
+          <t>보정점수 절단(100점 초과) 발생 건수 — ② U열 기준</t>
         </is>
       </c>
       <c r="B39" s="19">
-        <f>COUNTIF('평가군 계산'!$V$6:$V$79,"&lt;60")+COUNTIF('평가군 계산'!$V$6:$V$79,"&gt;100")</f>
+        <f>COUNTIF('평가군 계산'!$U$6:$U$79,"&gt;100")</f>
         <v/>
       </c>
       <c r="C39" s="19" t="n">
@@ -21445,11 +21447,11 @@
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>s(n) 표(n=2~16) 참고값 불일치 건수</t>
+          <t>제7호 조정 후 절단 발생 건수 — ② V열 기준</t>
         </is>
       </c>
       <c r="B40" s="19">
-        <f>COUNTIF('s(n) 표'!$AS$5:$AS$19,"FAIL")</f>
+        <f>COUNTIF('평가군 계산'!$V$6:$V$79,"&lt;60")+COUNTIF('평가군 계산'!$V$6:$V$79,"&gt;100")</f>
         <v/>
       </c>
       <c r="C40" s="19" t="n">
@@ -21463,11 +21465,11 @@
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>제7호 조정 총합계 (전 평가군)</t>
+          <t>s(n) 표(n=2~16) 참고값 불일치 건수</t>
         </is>
       </c>
       <c r="B41" s="19">
-        <f>ROUND(SUM('평가군 계산'!$N$6:$N$79),2)</f>
+        <f>COUNTIF('s(n) 표'!$AS$5:$AS$19,"FAIL")</f>
         <v/>
       </c>
       <c r="C41" s="19" t="n">
@@ -21478,124 +21480,102 @@
         <v/>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>제7호 조정 총합계 (전 평가군)</t>
+        </is>
+      </c>
+      <c r="B42" s="19">
+        <f>ROUND(SUM('평가군 계산'!$N$6:$N$79),2)</f>
+        <v/>
+      </c>
+      <c r="C42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="19">
+        <f>IF($B42=$C42,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>4. 등급 정원 합계 = 직급 인원 (규칙 제26조① · 최대잔여법) / [별표 10] 대조</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>직급</t>
         </is>
       </c>
-      <c r="B44" s="10" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>직급 인원</t>
         </is>
       </c>
-      <c r="C44" s="10" t="inlineStr">
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D44" s="10" t="inlineStr">
+      <c r="D45" s="10" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E44" s="10" t="inlineStr">
+      <c r="E45" s="10" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F44" s="10" t="inlineStr">
+      <c r="F45" s="10" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="G44" s="10" t="inlineStr">
+      <c r="G45" s="10" t="inlineStr">
         <is>
           <t>정원 합계</t>
         </is>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>판정</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>[별표 10] 대조</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="19" t="inlineStr">
-        <is>
-          <t>5급</t>
-        </is>
-      </c>
-      <c r="B45" s="19">
-        <f>'종합점수·등급'!$B$50</f>
-        <v/>
-      </c>
-      <c r="C45" s="19">
-        <f>'종합점수·등급'!$T$50</f>
-        <v/>
-      </c>
-      <c r="D45" s="19">
-        <f>'종합점수·등급'!$U$50</f>
-        <v/>
-      </c>
-      <c r="E45" s="19">
-        <f>'종합점수·등급'!$V$50</f>
-        <v/>
-      </c>
-      <c r="F45" s="19">
-        <f>'종합점수·등급'!$W$50</f>
-        <v/>
-      </c>
-      <c r="G45" s="19">
-        <f>SUM($C45:$F45)</f>
-        <v/>
-      </c>
-      <c r="H45" s="19">
-        <f>IF($G45=$B45,"PASS","FAIL")</f>
-        <v/>
-      </c>
-      <c r="I45" s="20" t="inlineStr">
-        <is>
-          <t>10명 이상 — [별표 10] 대상 아님</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="19" t="inlineStr">
         <is>
-          <t>4급</t>
+          <t>5급</t>
         </is>
       </c>
       <c r="B46" s="19">
-        <f>'종합점수·등급'!$B$51</f>
+        <f>'종합점수·등급'!$B$50</f>
         <v/>
       </c>
       <c r="C46" s="19">
-        <f>'종합점수·등급'!$T$51</f>
+        <f>'종합점수·등급'!$T$50</f>
         <v/>
       </c>
       <c r="D46" s="19">
-        <f>'종합점수·등급'!$U$51</f>
+        <f>'종합점수·등급'!$U$50</f>
         <v/>
       </c>
       <c r="E46" s="19">
-        <f>'종합점수·등급'!$V$51</f>
+        <f>'종합점수·등급'!$V$50</f>
         <v/>
       </c>
       <c r="F46" s="19">
-        <f>'종합점수·등급'!$W$51</f>
+        <f>'종합점수·등급'!$W$50</f>
         <v/>
       </c>
       <c r="G46" s="19">
@@ -21606,45 +21586,85 @@
         <f>IF($G46=$B46,"PASS","FAIL")</f>
         <v/>
       </c>
-      <c r="I46" s="20">
-        <f>IF(AND($B46=7,$C46=1,$D46=2,$E46=3,$F46=1),"PASS — [별표 10] 7명 행(1/2/3/1)과 일치","확인 필요")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="I46" s="20" t="inlineStr">
+        <is>
+          <t>10명 이상 — [별표 10] 대상 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>4급</t>
+        </is>
+      </c>
+      <c r="B47" s="19">
+        <f>'종합점수·등급'!$B$51</f>
+        <v/>
+      </c>
+      <c r="C47" s="19">
+        <f>'종합점수·등급'!$T$51</f>
+        <v/>
+      </c>
+      <c r="D47" s="19">
+        <f>'종합점수·등급'!$U$51</f>
+        <v/>
+      </c>
+      <c r="E47" s="19">
+        <f>'종합점수·등급'!$V$51</f>
+        <v/>
+      </c>
+      <c r="F47" s="19">
+        <f>'종합점수·등급'!$W$51</f>
+        <v/>
+      </c>
+      <c r="G47" s="19">
+        <f>SUM($C47:$F47)</f>
+        <v/>
+      </c>
+      <c r="H47" s="19">
+        <f>IF($G47=$B47,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="I47" s="20">
+        <f>IF(AND($B47=7,$C47=1,$D47=2,$E47=3,$F47=1),"PASS — [별표 10] 7명 행(1/2/3/1)과 일치","확인 필요")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>5. 1차·2차 평가자 간 순위 일치도 (스피어만) — 규칙 제9조⑥2호 보고 항목</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>평가군 5(1차 4급 7명) 과 평가군 6(2차 4급 7명) 의 순위상관</t>
         </is>
       </c>
-      <c r="B49" s="23">
+      <c r="B50" s="23">
         <f>ROUND(CORREL('평가군 계산'!$H$66:$H$72,'평가군 계산'!$H$73:$H$79),4)</f>
         <v/>
       </c>
-      <c r="C49" s="15" t="inlineStr">
+      <c r="C50" s="15" t="inlineStr">
         <is>
           <t>순위끼리의 피어슨 상관 = 스피어만 ρ. 동점이 없으므로 이 등식이 성립한다.</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>6. 종합 판정</t>
         </is>
       </c>
-      <c r="B51" s="32">
-        <f>IF(AND(COUNTIF($E$7:$E$12,"FAIL")=0,COUNTIF($H$7:$H$12,"FAIL")=0,COUNTIF($K$7:$K$12,"FAIL")=0,COUNTIF($F$27:$F$30,"FAIL")=0,COUNTIF($D$35:$D$41,"FAIL")=0,COUNTIF($H$45:$H$46,"FAIL")=0),"PASS — 전 항목 통과","FAIL — 위 항목 확인")</f>
-        <v/>
-      </c>
-      <c r="C51" s="15" t="inlineStr">
+      <c r="B52" s="32">
+        <f>IF(AND(COUNTIF($E$7:$E$12,"FAIL")=0,COUNTIF($H$7:$H$12,"FAIL")=0,COUNTIF($K$7:$K$12,"FAIL")=0,COUNTIF($F$28:$F$31,"FAIL")=0,COUNTIF($D$36:$D$42,"FAIL")=0,COUNTIF($H$46:$H$47,"FAIL")=0),"PASS — 전 항목 통과","FAIL — 위 항목 확인")</f>
+        <v/>
+      </c>
+      <c r="C52" s="15" t="inlineStr">
         <is>
           <t>① 평가군별 평균·표준편차·조정 합계  ② ÷s(n) 효과  ③ 순위 보존·절단·동점·s(n) 표  ④ 등급 정원</t>
         </is>
@@ -21652,10 +21672,10 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A24:H24"/>
     <mergeCell ref="A16:H16"/>
   </mergeCells>
-  <conditionalFormatting sqref="D7:D53">
+  <conditionalFormatting sqref="D7:D54">
     <cfRule type="cellIs" priority="1" operator="containsText" dxfId="0">
       <formula>NOT(ISERROR(SEARCH("PASS",D7)))</formula>
     </cfRule>
@@ -21663,7 +21683,7 @@
       <formula>NOT(ISERROR(SEARCH("FAIL",D7)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E7:E53">
+  <conditionalFormatting sqref="E7:E54">
     <cfRule type="cellIs" priority="3" operator="containsText" dxfId="0">
       <formula>NOT(ISERROR(SEARCH("PASS",E7)))</formula>
     </cfRule>
@@ -21671,7 +21691,7 @@
       <formula>NOT(ISERROR(SEARCH("FAIL",E7)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F53">
+  <conditionalFormatting sqref="F7:F54">
     <cfRule type="cellIs" priority="5" operator="containsText" dxfId="0">
       <formula>NOT(ISERROR(SEARCH("PASS",F7)))</formula>
     </cfRule>
@@ -21679,7 +21699,7 @@
       <formula>NOT(ISERROR(SEARCH("FAIL",F7)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G7:G53">
+  <conditionalFormatting sqref="G7:G54">
     <cfRule type="cellIs" priority="7" operator="containsText" dxfId="0">
       <formula>NOT(ISERROR(SEARCH("PASS",G7)))</formula>
     </cfRule>
@@ -21687,7 +21707,7 @@
       <formula>NOT(ISERROR(SEARCH("FAIL",G7)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H7:H53">
+  <conditionalFormatting sqref="H7:H54">
     <cfRule type="cellIs" priority="9" operator="containsText" dxfId="0">
       <formula>NOT(ISERROR(SEARCH("PASS",H7)))</formula>
     </cfRule>
@@ -21695,7 +21715,7 @@
       <formula>NOT(ISERROR(SEARCH("FAIL",H7)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I7:I53">
+  <conditionalFormatting sqref="I7:I54">
     <cfRule type="cellIs" priority="11" operator="containsText" dxfId="0">
       <formula>NOT(ISERROR(SEARCH("PASS",I7)))</formula>
     </cfRule>
@@ -21703,7 +21723,7 @@
       <formula>NOT(ISERROR(SEARCH("FAIL",I7)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J7:J53">
+  <conditionalFormatting sqref="J7:J54">
     <cfRule type="cellIs" priority="13" operator="containsText" dxfId="0">
       <formula>NOT(ISERROR(SEARCH("PASS",J7)))</formula>
     </cfRule>
@@ -21711,7 +21731,7 @@
       <formula>NOT(ISERROR(SEARCH("FAIL",J7)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K7:K53">
+  <conditionalFormatting sqref="K7:K54">
     <cfRule type="cellIs" priority="15" operator="containsText" dxfId="0">
       <formula>NOT(ISERROR(SEARCH("PASS",K7)))</formula>
     </cfRule>
@@ -21719,7 +21739,7 @@
       <formula>NOT(ISERROR(SEARCH("FAIL",K7)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7:B53">
+  <conditionalFormatting sqref="B7:B54">
     <cfRule type="cellIs" priority="17" operator="containsText" dxfId="0">
       <formula>NOT(ISERROR(SEARCH("PASS",B7)))</formula>
     </cfRule>
@@ -21868,7 +21888,7 @@
         <v/>
       </c>
       <c r="E8" s="23">
-        <f>IF($C8&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C8,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C8,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="F8" s="23">
@@ -21913,7 +21933,7 @@
         <v/>
       </c>
       <c r="E9" s="23">
-        <f>IF($C9&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C9,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C9,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="F9" s="23">
@@ -21958,7 +21978,7 @@
         <v/>
       </c>
       <c r="E10" s="23">
-        <f>IF($C10&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C10,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C10,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="F10" s="23">
@@ -22003,7 +22023,7 @@
         <v/>
       </c>
       <c r="E11" s="23">
-        <f>IF($C11&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C11,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C11,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="F11" s="23">
@@ -22048,7 +22068,7 @@
         <v/>
       </c>
       <c r="E12" s="23">
-        <f>IF($C12&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C12,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C12,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="F12" s="23">
@@ -22093,7 +22113,7 @@
         <v/>
       </c>
       <c r="E13" s="23">
-        <f>IF($C13&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C13,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C13,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="F13" s="23">
@@ -22138,7 +22158,7 @@
         <v/>
       </c>
       <c r="E14" s="23">
-        <f>IF($C14&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C14,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C14,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="F14" s="23">
@@ -22183,7 +22203,7 @@
         <v/>
       </c>
       <c r="E15" s="23">
-        <f>IF($C15&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C15,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C15,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="F15" s="23">
@@ -22228,7 +22248,7 @@
         <v/>
       </c>
       <c r="E16" s="23">
-        <f>IF($C16&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C16,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C16,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="F16" s="23">
@@ -22273,7 +22293,7 @@
         <v/>
       </c>
       <c r="E17" s="23">
-        <f>IF($C17&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C17,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C17,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="F17" s="23">
@@ -22454,7 +22474,7 @@
         <v/>
       </c>
       <c r="E26" s="23">
-        <f>IF($C26&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C26,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C26,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="F26" s="23">
@@ -22492,7 +22512,7 @@
         <v/>
       </c>
       <c r="E27" s="23">
-        <f>IF($C27&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C27,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C27,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="F27" s="23">
@@ -22530,7 +22550,7 @@
         <v/>
       </c>
       <c r="E28" s="23">
-        <f>IF($C28&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C28,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C28,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="F28" s="23">
@@ -22568,7 +22588,7 @@
         <v/>
       </c>
       <c r="E29" s="23">
-        <f>IF($C29&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C29,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C29,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="F29" s="23">
@@ -22715,7 +22735,7 @@
         <v>31</v>
       </c>
       <c r="E37" s="23">
-        <f>IF($C37&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C37,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C37,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="F37" s="24">
@@ -22746,7 +22766,7 @@
         <v>22</v>
       </c>
       <c r="E38" s="23">
-        <f>IF($C38&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C38,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C38,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="F38" s="24">
@@ -22777,7 +22797,7 @@
         <v>13</v>
       </c>
       <c r="E39" s="23">
-        <f>IF($C39&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C39,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C39,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="F39" s="24">
@@ -22808,7 +22828,7 @@
         <v>6</v>
       </c>
       <c r="E40" s="23">
-        <f>IF($C40&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C40,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C40,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="F40" s="24">
@@ -22940,7 +22960,7 @@
         <v/>
       </c>
       <c r="E48" s="23">
-        <f>IF($C48&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C48,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C48,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="F48" s="23">
@@ -22982,7 +23002,7 @@
         <v/>
       </c>
       <c r="E49" s="23">
-        <f>IF($C49&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C49,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C49,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="F49" s="23">
@@ -23024,7 +23044,7 @@
         <v/>
       </c>
       <c r="E50" s="23">
-        <f>IF($C50&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C50,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C50,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="F50" s="23">
@@ -23066,7 +23086,7 @@
         <v/>
       </c>
       <c r="E51" s="23">
-        <f>IF($C51&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C51,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C51,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="F51" s="23">
@@ -23108,7 +23128,7 @@
         <v/>
       </c>
       <c r="E52" s="23">
-        <f>IF($C52&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C52,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C52,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="F52" s="23">
@@ -23150,7 +23170,7 @@
         <v/>
       </c>
       <c r="E53" s="23">
-        <f>IF($C53&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C53,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C53,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="F53" s="23">
@@ -23192,7 +23212,7 @@
         <v/>
       </c>
       <c r="E54" s="23">
-        <f>IF($C54&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C54,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C54,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="F54" s="23">
@@ -23234,7 +23254,7 @@
         <v/>
       </c>
       <c r="E55" s="23">
-        <f>IF($C55&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C55,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C55,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="F55" s="23">
@@ -23276,7 +23296,7 @@
         <v/>
       </c>
       <c r="E56" s="23">
-        <f>IF($C56&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C56,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C56,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="F56" s="23">
@@ -23318,7 +23338,7 @@
         <v/>
       </c>
       <c r="E57" s="23">
-        <f>IF($C57&gt;=17,1,INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C57,'s(n) 표'!$A$5:$A$43,0)))</f>
+        <f>INDEX('s(n) 표'!$AQ$5:$AQ$43,MATCH($C57,'s(n) 표'!$A$5:$A$43,0))</f>
         <v/>
       </c>
       <c r="F57" s="23">
